--- a/artfynd/A 10632-2023 artfynd.xlsx
+++ b/artfynd/A 10632-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10632-2023 artfynd.xlsx
+++ b/artfynd/A 10632-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107312711</v>
+        <v>107312704</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,11 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406200.7172868281</v>
+        <v>406340</v>
       </c>
       <c r="R2" t="n">
-        <v>7050454.853232461</v>
+        <v>7050262</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +747,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107312707</v>
+        <v>107312705</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,11 +812,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -848,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406257.8198756955</v>
+        <v>406328</v>
       </c>
       <c r="R3" t="n">
-        <v>7050302.491388028</v>
+        <v>7050274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,19 +853,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -925,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107312710</v>
+        <v>107312706</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406218.04486443</v>
+        <v>406269</v>
       </c>
       <c r="R4" t="n">
-        <v>7050452.112664741</v>
+        <v>7050297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,19 +959,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1046,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107312709</v>
+        <v>107312707</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1024,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406234.3809939134</v>
+        <v>406258</v>
       </c>
       <c r="R5" t="n">
-        <v>7050340.184205919</v>
+        <v>7050302</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,19 +1069,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1167,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107312705</v>
+        <v>107312708</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1134,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1211,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406327.9727052732</v>
+        <v>406241</v>
       </c>
       <c r="R6" t="n">
-        <v>7050274.565408207</v>
+        <v>7050293</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,19 +1179,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1288,15 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107312706</v>
+        <v>107312709</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406268.8122554798</v>
+        <v>406234</v>
       </c>
       <c r="R7" t="n">
-        <v>7050296.817416103</v>
+        <v>7050340</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,19 +1285,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1409,15 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107312708</v>
+        <v>107312710</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,11 +1350,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1457,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406241.0284710776</v>
+        <v>406218</v>
       </c>
       <c r="R8" t="n">
-        <v>7050293.179438294</v>
+        <v>7050452</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1490,19 +1391,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1534,15 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107312704</v>
+        <v>107312711</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1456,11 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1578,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406340.1194531578</v>
+        <v>406201</v>
       </c>
       <c r="R9" t="n">
-        <v>7050262.616380218</v>
+        <v>7050455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1611,19 +1501,9 @@
           <t>2023-03-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 10632-2023 artfynd.xlsx
+++ b/artfynd/A 10632-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312704</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312706</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312707</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312708</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312709</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312710</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,8 +1572,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107312711</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>